--- a/hunting/checklists/IR_CHECKLIST_ROLES.xlsx
+++ b/hunting/checklists/IR_CHECKLIST_ROLES.xlsx
@@ -13,6 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database server" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain controller" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="File server" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AWS account" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AWS web app" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AWS network" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Baseline'!$A$3:$K$60</definedName>
@@ -21,6 +24,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Database server'!$A$3:$K$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Domain controller'!$A$3:$K$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'File server'!$A$3:$K$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'AWS account'!$A$3:$K$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'AWS web app'!$A$3:$K$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'AWS network'!$A$3:$K$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -6154,4 +6160,2113 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Project &lt;name&gt;  AWS account (CloudTrail) checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Every AWS account in scope, from its CloudTrail logs (aws-cloudtrail-*). Load each account (or each trail) with its own --source, so every row shows which account it came from in _index. The usual questions: how did the attacker get credentials or a session, what did those principals do, did they keep access, and did they take, destroy or hide anything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Tasked to</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Handover From</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Handover to</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Handover Date</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Queries</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>IR ref</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Account profile</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Which accounts, regions and time range the loaded CloudTrail covers</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Gaps in the time range (trail stopped, regions not logged); whether S3 data events exist (event_category Data) for rows 5.1 and 7.3.</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>ATRI-01</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>1.2.3, 2.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Principals that call the APIs, and from where</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Expected automation (CI roles, AWS services) versus people; principals with many failures; the known-good source ranges for later rows.</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>ATRI-02</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>1.2.4, 1.3.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Privileged identities, break-glass accounts and the organisation's known-good IP ranges</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Ask the client: who should hold AdministratorAccess, which roles are assumed from which accounts, which corporate egress addresses and VPN ranges are normal.</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>1.3.2 to 1.3.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Regions the account normally uses</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>API calls in regions nobody uses are a common sign of crypto-mining or hidden resources.</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>ADE-02</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>1.2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Initial access</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
+      <c r="K9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Console sign-ins: root, no MFA, failures, new sources</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Root sign-ins; sign-ins without MFA; successful sign-ins from addresses outside the known-good ranges, especially right after failures.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>AIA-01</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>2.4.3, 2.4.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Brute force and password spraying against the console</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>One source failing for many users, or one user failing from many sources, followed by a success.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>AIA-02</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>2.4.1, 2.4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Long-term access keys used from new places or with new tooling</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>An AKIA... key suddenly used from a VPS or Tor address, or with a user agent such as Kali, Pacu, ScoutSuite or an odd SDK version.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>AIA-03</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>2.4.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Instance role credentials used outside the instance</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>The same EC2 role session used from several addresses, one of them public: credentials stolen through SSRF or from the metadata service.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>ACA-02</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>2.4.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Discovery and probing</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Enumeration bursts</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Dozens of List/Describe/Get calls across services within minutes: someone mapping what the key can see.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>ADI-01</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>2.4.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Permission probing</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>AccessDenied and UnauthorizedOperation errors across many services from one principal.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>ADI-02</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>2.4.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Privilege escalation, persistence and lateral movement</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>IAM policy escalation</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Admin policies attached, new default policy versions, permission boundaries removed, inline policies with *:*.</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>APR-01</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>2.4.18 to 2.4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>New IAM users, access keys, passwords and MFA changes</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Users and keys created by a suspicious principal; login profiles added to service users; MFA devices removed.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>APE-01</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>2.4.18 to 2.4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Role trust and federation backdoors</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Trust policies that let an outside account or * assume a role; new SAML/OIDC providers; IAM Identity Center changes.</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>APE-02</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>2.4.18 to 2.4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Role assumption and cross-account access</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Chains of AssumeRole from the compromised principal; roles assumed from accounts outside the organisation.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>ALM-01</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>2.4.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Code run on workloads through AWS APIs</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>SSM SendCommand/StartSession, user data changes, EC2 Instance Connect keys, new Lambda code, ECS task definitions and CloudFormation stacks from the suspicious principal.</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>AEX-01</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>2.4.5, 2.4.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Credential access and collection</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
+      <c r="K23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Secrets, parameters and EC2 passwords retrieved</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>GetSecretValue, GetParameter(s) with decryption and GetPasswordData by principals that do not normally read them.</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>ACA-01</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>2.4.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>S3 reads and listings per principal and bucket</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Large GetObject counts or byte totals from one principal or source; needs S3 data events.</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>ACO-01</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>2.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Defense impairment</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Logging and security services stopped or weakened</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>StopLogging, DeleteTrail, event selectors reduced, GuardDuty detectors or Security Hub disabled, Config recorders stopped, flow logs deleted.</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>ADE-01</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>2.4.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Network exposure changes</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Security groups or network ACLs opened to 0.0.0.0/0, new internet gateways and routes, public RDS instances.</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>ADE-03</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>2.4.26, 2.4.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Exfiltration and impact</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Snapshots, images, buckets and keys shared or made public</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>ModifySnapshotAttribute/ModifyImageAttribute with another account, bucket policies or ACLs that grant public or foreign access, KMS grants to outside accounts.</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>AEXF-01</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>2.4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Destructive actions, ransom-style encryption and resource hijacking</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Mass deletion of buckets, snapshots and backups; S3 objects re-encrypted with an outside KMS key; many large instances started (mining).</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>AIM-01</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>2.1.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Not covered by these queries</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>CloudTrail S3 data events and Lambda invoke events are only there if the trail logged them; without them rows 5.2 and parts of 7.2 have no data.</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>GuardDuty findings, Security Hub, IAM credential reports and Access Advisor data: export them separately, they help confirm rows 2.3, 2.4 and 4.1.</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Activity inside instances (process, logon and file artifacts): collect the hosts and use the Windows checklists, or Linux triage outside this toolkit.</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>S3 server access logs and CloudFront logs are not loaded by this toolkit.</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:K37"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="D5 D6 D7 D8 D10 D11 D12 D13 D15 D16 D18 D19 D20 D21 D22 D24 D25 D27 D28 D30 D31 D34 D35 D36 D37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not started,In progress,Done,Not applicable,No data"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Project &lt;name&gt;  AWS web application (ALB and WAF) checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Internet-facing applications behind an Application Load Balancer or Classic ELB (aws-alb-*) and protected by AWS WAF (aws-waf-*). Run the account checklist for the account as well. The usual questions: was the application exploited, did a web shell or stolen session follow, and how much data left through the front door.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Tasked to</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Handover From</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Handover to</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Handover Date</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Queries</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>IR ref</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Application profile</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Which load balancers and web ACLs were loaded, and for which time range</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>One _index per evidence source; the load balancer names and web ACL names in the data; gaps in the time range.</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>ATRI-01</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>1.2.3, 2.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>What sits behind the load balancer, and what the WAF is set to block or count</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Ask the client for the target groups, the application stack and versions, and which WAF rules are in Count mode. Count-mode rules log a match but let the request through.</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>1.3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Exploitation attempts</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Exploitation attempts in the load balancer logs, per client</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>SQL injection, path traversal, Log4Shell/JNDI, template injection and scanner user agents; the clients with the highest scores and the status codes they got (2xx after many 4xx matters).</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>AIA-04</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>2.4, 2.4.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>WAF blocked clients, and what the same clients got through</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Clients blocked many times that also have ALLOW requests: the WAF caught some of the attack, not all.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>AIA-05</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>2.4, 2.4.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>WAF rules that matched but did not block</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Managed rules in Count mode and labels on allowed requests (SQLi, bad inputs, known bad IPs): those requests reached the application.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>AIA-06</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Web shells and follow-on</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Script files reached by very few clients</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>.php, .jsp, .aspx paths requested by one or two clients, especially with POST and 200, and paths in upload folders.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>APE-03</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>2.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Large responses per client</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Clients that downloaded far more than others: data dumps, backups or export endpoints abused.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>AEXF-03</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>2.4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>The targets' outbound traffic after the exploitation time</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>From the VPC flow logs: the target instances connecting out to new public addresses after row 2.1's timestamps (see the VPC checklist).</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>AEXF-02, AC2-01</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>2.4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Not covered by these queries</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Application logs on the targets (web server access and error logs, framework logs): the request body is not in ALB logs, and WAF logs carry headers but not the body.</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>CloudFront and API Gateway access logs are not loaded by this toolkit. WAF logs from CloudFront or API Gateway web ACLs are (http_source_name says which).</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>The ALB client:port is the real client only when nothing sits in front of the load balancer; behind CloudFront or another proxy, use the WAF xff.ip or the proxy's own logs.</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Network Load Balancer access logs and ALB connection logs are skipped by the importer.</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:K20"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="D5 D6 D8 D9 D10 D12 D13 D14 D17 D18 D19 D20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not started,In progress,Done,Not applicable,No data"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Project &lt;name&gt;  AWS network (VPC Flow Logs) checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>VPC Flow Logs (aws-vpcflow-*) for the VPCs, subnets or interfaces in scope. The usual questions: was something scanned or reached from the internet, did the attacker move between instances, and is anything beaconing out or sending data out. Flow logs carry addresses, ports, byte counts and accept/reject only, so every row is a lead to confirm on the hosts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Tasked to</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Handover From</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Handover to</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Handover Date</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Queries</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>IR ref</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Which interfaces, accounts and time range the flow logs cover</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Whether the flow logs capture ALL traffic or only REJECT, and the aggregation interval (1 or 10 minutes); gaps in the time range.</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>ATRI-01</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>1.2.3, 2.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Internal address ranges, NAT gateways and known-good destinations</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Ask the client for the VPC CIDRs, NAT gateway and load balancer interfaces, and expected external services (update servers, SaaS, partners).</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>1.3.1, 1.3.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Inbound traffic from the internet: scanners and what they reached</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Public sources touching many ports or hosts; accepted inbound connections on management ports (22, 3389, 5985, databases).</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>ADI-04</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>2.4.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Inside the VPC</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
+      <c r="K9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Internal scanning</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>One internal source reaching many hosts or ports, especially a web or jump host.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>ADI-03</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>2.4.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>East-west administrative connections</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>SSH, RDP, SMB, WinRM and database connections between instances that do not normally talk.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>ALM-02</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>2.4.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Beacon-like outbound connections</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>One instance reaching one rare public address in most hours, with small, regular byte counts.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>AC2-01</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>2.4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Uncommon and known-bad outbound ports</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Tor, mining-pool and reverse-shell ports; anything outbound from instances that should only answer requests.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>AC2-02</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>2.4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Large outbound transfers to public addresses</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Byte totals far above the instance's usual; compare the time with S3 access (ACO-01) and ALB downloads (AEXF-03).</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>AEXF-02</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>2.4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Not covered by these queries</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Packet contents, DNS queries and TLS server names: flow logs do not have them. Route 53 Resolver query logs and Traffic Mirroring are outside this toolkit.</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Flow logs in Parquet format are not read; deliver them as text or convert them first.</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Traffic to and from the instance metadata service, Amazon DNS and the time service is never logged by AWS.</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:K20"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="D5 D6 D8 D10 D11 D13 D14 D15 D18 D19 D20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not started,In progress,Done,Not applicable,No data"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/hunting/checklists/IR_CHECKLIST_ROLES.xlsx
+++ b/hunting/checklists/IR_CHECKLIST_ROLES.xlsx
@@ -7239,7 +7239,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Internet-facing applications behind an Application Load Balancer or Classic ELB (aws-alb-*) and protected by AWS WAF (aws-waf-*). Run the account checklist for the account as well. The usual questions: was the application exploited, did a web shell or stolen session follow, and how much data left through the front door.</t>
+          <t>Internet-facing applications behind an Application Load Balancer or Classic ELB and protected by AWS WAF (aws-waf-*). ALB logs are loaded into httpdlog-&lt;source&gt;, next to any IIS, NGINX or Apache access logs in httpdlog-*, so rows 2.1, 3.1 and 3.2 hunt across all web front ends at once. Run the account checklist for the account as well. The usual questions: was the application exploited, did a web shell or stolen session follow, and how much data left through the front door.</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Exploitation attempts in the load balancer logs, per client</t>
+          <t>Exploitation attempts in the web access logs (ALB/ELB and other web servers), per client</t>
         </is>
       </c>
       <c r="C8" s="5" t="n"/>
@@ -7532,7 +7532,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Script files reached by very few clients</t>
+          <t>Script pages reached by very few clients</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>

--- a/hunting/checklists/IR_CHECKLIST_ROLES.xlsx
+++ b/hunting/checklists/IR_CHECKLIST_ROLES.xlsx
@@ -16,6 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AWS account" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AWS web app" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AWS network" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Linux baseline" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Linux internet-facing" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Baseline'!$A$3:$K$60</definedName>
@@ -27,6 +29,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'AWS account'!$A$3:$K$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'AWS web app'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'AWS network'!$A$3:$K$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Linux baseline'!$A$3:$K$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Linux internet-facing'!$A$3:$K$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2243,6 +2247,1783 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Project &lt;name&gt;  Baseline: all Linux hosts checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Every Linux host loaded with the Linux importers (Linux/linux2sofelk.py on a UAC collection or a collected root filesystem), before the role checklist. The order follows an intrusion: what evidence exists, who logged in, what ran, what was left behind to come back, and what was done to hide it. Set the since line in the queries that have one to the start of the incident window. The IR ref column points to the closest item of the IR checklist, which is written for Windows hosts, and is blank where nothing fits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Tasked to</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Handover From</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Handover to</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Handover Date</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Queries</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>IR ref</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Evidence and host profile</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Which Linux sources were loaded and how far back the logs reach</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>No auditd.log means no full command-line record; no journal or syslog rows means the logs were not exported. Compare the oldest log entry with the incident window.</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>LTRI-01</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>1.2.3, 2.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Boots, shutdowns, crashes and log gaps</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Boots with no journal, journals that stop early, crashes; a kernel change outside an upgrade.</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>LTRI-02</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>2.4.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Accounts, their rights and their activity</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Accounts that can log in, uid0 and empty-password flags, accounts changed by the last edit of /etc/passwd, service accounts with logins.</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>LTRI-03</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>1.3.2, 2.4.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Software installed and removed</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Attack tools, compilers, removed security packages, local .deb/.rpm installs inside the window.</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>LTRI-04</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>1.2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Access</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
+      <c r="K9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Logins from the internet</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Successful logins from public addresses, above all after failures.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>LIA-01</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>2.4.3, 2.4.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Brute force and spraying</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Sources that failed and then succeeded; internal sources spraying.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>LCA-01</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>2.4.1, 2.4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Remote sessions in and out</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Logins from other servers, long or still-open sessions; SSH, RDP and SMB clients run from this host, known_hosts growth.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>LLM-01, LLM-02</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>2.4.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>SSH keys</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Keys added to root or a service account, logins with keys no longer on disk.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>LPE-04</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>2.4.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Execution and privilege</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Commands run with sudo, su and pkexec</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Root shells, downloads, edits of system files, refused attempts.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>LEX-01, LPR-01</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>2.1.1, 2.4.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Suspicious command lines</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Download-and-run, encoded commands, interpreter one-liners, reverse shells and tunnels.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>LEX-04, LC2-01</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>2.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Programs in temporary, hidden and user-writable folders</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Executables in /tmp or /dev/shm, processes running from deleted binaries, kernel-thread names on disk.</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>LEX-02, LEX-03, LDE-04</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>2.1.1, 2.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Discovery and scanning</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Bursts of discovery commands, enumeration scripts, scanners and their output.</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>LDI-01, LDI-02, LDI-03</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>2.4.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Setuid files, privileged groups and sudoers</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Setuid shells, users added to sudo/wheel/docker, NOPASSWD rules.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>LPR-02, LPR-03</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>2.4.19, 2.4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Credential access</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>/etc/shadow read, private keys and tickets outside their place, cracking and sniffing tools.</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>LCA-02</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>2.4.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>systemd services and timers</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Admin units running from odd folders, units enabled in the window, transient run-* units.</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>LPE-01</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>2.4.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Cron and at jobs</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Jobs in user crontabs, jobs that ran but are gone, downloads in jobs.</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>LPE-02</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>2.4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Shell startup files and init scripts</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Aliases wrapping sudo/ssh, PROMPT_COMMAND, network tools in .bashrc, autostart entries in home folders.</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>LPE-03, LPE-10</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>2.1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Accounts and groups changed</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>New accounts, new members of privileged groups, /etc/shadow changes with no log line.</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>LPE-05</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>2.4.18 to 2.4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Loader and kernel</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>/etc/ld.so.preload, LD_PRELOAD in units or sudoers, out-of-tree modules, .ko files outside the module tree.</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>LPE-06, LPE-08</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>2.1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Package sources</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Unsigned repositories, keys added in the window, packages installed from files.</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>LPE-09</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>1.2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Command and control, collection and exfiltration</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Downloads and suspicious URLs</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Payload fetches by curl/wget, new executables in /tmp or Downloads, URLs on IPs or tunnelling services.</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>LC2-03, LIA-03</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>2.4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Outbound destinations and name resolution</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Rare destinations, OpenVPN endpoints, hosts-file and resolver changes, system proxies.</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>LC2-02, LC2-04</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>2.4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Staging and exfiltration</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Archives in temporary or web folders, rclone/curl -T/scp uploads, file-sharing sites.</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>LCO-01, LCO-02, LEXF-01, LEXF-02</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>2.1.4, 2.4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Impact and defense impairment</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Destruction, ransomware and miners</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Wiping commands, ransom notes and extension bursts, miner binaries and pools.</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>LIM-01, LIM-02, LIM-03</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>2.1.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Logs and history tampered</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>History linked to /dev/null, emptied logs, journald and rsyslog stopped by hand.</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>LDE-01</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>2.4.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Security tools disabled</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>auditd, AppArmor, SELinux, firewalls and EDR agents stopped, masked or removed.</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>LDE-02</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>2.4.21, 2.4.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Timestomping and clock changes</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>ctime before mtime, backdated files in cron and systemd folders, touch -d, clock set by hand.</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>LDE-03</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>2.1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Not covered by these queries</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="4" t="n"/>
+      <c r="K38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Commands typed in a shell without sudo on a host without auditd: they are logged nowhere the toolkit loads. Read .bash_history, .zsh_history and similar files by hand (no timestamps unless HISTTIMEFORMAT was set).</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>UAC live_response output (running processes, open connections, lsof, /proc dumps) and memory images: read them directly.</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Container runtimes (Docker, containerd, Kubernetes) beyond what the host's journal holds, and application logs other than web and FTP servers.</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:K41"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="D5 D6 D7 D8 D10 D11 D12 D13 D15 D16 D17 D18 D19 D20 D22 D23 D24 D25 D26 D27 D29 D30 D31 D33 D34 D35 D36 D39 D40 D41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not started,In progress,Done,Not applicable,No data"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Project &lt;name&gt;  Linux internet-facing server checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Linux hosts that expose a service to the internet: web servers and applications behind them, SSH bastions, FTP servers, VPN gateways. Run the baseline first. These rows add the attack paths that come through the exposed service. The IR ref column is approximate (the IR checklist is written for Windows hosts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Tasked to</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Handover From</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Handover to</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Handover Date</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Queries</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>IR ref</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>The exposed service</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Which logs exist for the exposed services</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>apache.access, nginx.access, ftp.*, sshd lines; the time range of each.</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>LTRI-01</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>1.2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Web server, application and their versions</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Product and version of the web server, CMS or framework against known exploited CVEs; packages installed outside the repositories.</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>LTRI-04, LPE-09</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>1.2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Initial access through the service</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Web exploitation attempts and what got a 2xx</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Traversal, injection and probes answered with 200; scanner and curl/wget user agents.</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>LIA-02</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Web shells</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Small, new scripts in the web root owned by the web server account and requested by one or two clients, mostly by POST.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>LPE-07</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>2.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>SSH and FTP brute force and logins</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Success after failures; FTP logins from the internet.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>LCA-01, LIA-01</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>2.4.1 to 2.4.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>After exploitation</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>What the service account ran</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Programs in the web root or /tmp run as www-data/apache/nginx; discovery right after the first 2xx exploit.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>LEX-02, LEX-04, LDI-01</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>2.1.1, 2.4.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Reverse shells, tunnels and downloads</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>bash -i &gt;&amp; /dev/tcp, chisel/ligolo agents, payloads fetched into /tmp or served by this host.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>LC2-01, LC2-03</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>2.4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Persistence beyond the web shell</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Units, cron jobs and SSH keys added around the exploitation time.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>LPE-01, LPE-02, LPE-04</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>2.4.14, 2.4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Miners</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Miner binaries, pools in command lines, OOM kills; the most common outcome of a mass-exploited web or Redis/Docker service.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>LIM-03</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>2.1.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Data pulled through the service</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Archives and database dumps in the web root, and the clients that downloaded them; large FTP downloads.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>LCO-01, LEXF-03</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>2.4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Pivoting into the internal network</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>SSH and SMB from this host to internal hosts, internal scans.</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>LLM-02, LDI-03</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>2.4.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Not covered by these queries</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Application logs other than Apache, nginx, lighttpd and FTP access logs (PHP-FPM, Tomcat, application frameworks, databases), WAF and reverse-proxy logs in front of the server, and the web root's content itself (read suspicious scripts from the collection).</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:K20"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="D5 D6 D8 D9 D10 D12 D13 D14 D15 D16 D17 D20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not started,In progress,Done,Not applicable,No data"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
